--- a/DesignTable/Data/Table/Tables/monster_boss.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_boss.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oh\Desktop\DesignGenerator\Data\Data_Export\Table\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F0B9B51-D09A-4AEC-83BA-A0B4A668BD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F74FD1DC-58B7-408A-9515-044B51706EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-240" yWindow="0" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{56D7624B-7CB0-48D9-93FE-DC8F942FF1A2}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{56D7624B-7CB0-48D9-93FE-DC8F942FF1A2}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>mon_id</t>
   </si>
   <si>
@@ -125,6 +121,14 @@
   </si>
   <si>
     <t>mon_spawnDayNight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -182,7 +186,11 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -197,7 +205,7 @@
 
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
+  <Schema ID="Schema2">
     <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
       <xsd:element nillable="true" name="monster_boss">
         <xsd:complexType>
@@ -212,6 +220,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -232,7 +241,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="1" Name="monster_boss_맵" RootElement="monster_boss" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="4" Name="monster_boss_맵" RootElement="monster_boss" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -241,22 +250,22 @@
   <autoFilter ref="A1:F2" xr:uid="{219B2AB9-71B2-43D2-AE6E-1611D13DCF23}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{AD9B9425-01B9-40D9-AE72-DCBA99B5D621}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{059D2B67-4C83-46B2-B4BD-4EDE35F38133}" uniqueName="mon_pathId" name="mon_pathId">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/record/mon_pathId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_pathId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{C1772F7D-DD8E-4A36-8690-D1347E3B9C42}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{99E00AF6-8AF3-496F-B170-52EB1B72FD9E}" uniqueName="mon_spawnId" name="mon_spawnId">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/record/mon_spawnId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_spawnId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{82B7969F-C8B2-40F9-BD70-BD083F72D236}" uniqueName="mon_spawnTime" name="mon_spawnTime">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/record/mon_spawnTime" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_spawnTime" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{990746DB-2815-4B16-8C7D-4B45AA5C32E1}" uniqueName="mon_spawnDayNight" name="mon_spawnDayNight">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/record/mon_spawnDayNight" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_spawnDayNight" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -264,35 +273,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{45C7799A-8301-4E60-B2D0-3DE51CA51E51}" name="표1" displayName="표1" ref="A1:I7" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I7" xr:uid="{45C7799A-8301-4E60-B2D0-3DE51CA51E51}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{45C7799A-8301-4E60-B2D0-3DE51CA51E51}" name="표1" displayName="표1" ref="A1:J7" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J7" xr:uid="{45C7799A-8301-4E60-B2D0-3DE51CA51E51}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{77EAA5DA-E1F1-421E-ACC8-93692512F11D}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8DBAF7B5-5E74-4090-92E0-20C16DFD816F}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{78F3970B-3EF8-4355-97B6-FB2E214E6683}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7E847E13-3429-4541-8B7B-6EDF5C718DD3}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{6E681DF7-C625-4327-BEB2-EB7DFE49CCF1}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{A51832D6-4DA9-400F-9ADB-89F73082B709}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{D2A8E0C7-292E-4CBA-B874-D84552D516DB}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{88DB5186-CA75-44DE-93BD-FD7BE3E772C3}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{25330282-8179-436F-8B54-8CEA5B97079F}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="1" xpath="/monster_boss/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{25330282-8179-436F-8B54-8CEA5B97079F}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{795533A2-BE81-4D94-8F02-1FDF3308FE99}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -601,22 +613,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -638,10 +650,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12321440-48D0-4C1B-BC63-0C54B3150208}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -667,180 +679,201 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1018</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="1">
         <v>1018</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="1">
         <v>1018</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="1">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="1">
         <v>1018</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/monster_boss.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_boss.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F74FD1DC-58B7-408A-9515-044B51706EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38D8870A-2911-4A73-B069-19F0F30744B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{56D7624B-7CB0-48D9-93FE-DC8F942FF1A2}"/>
   </bookViews>
@@ -241,7 +241,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="4" Name="monster_boss_맵" RootElement="monster_boss" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="6" Name="monster_boss_맵" RootElement="monster_boss" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -250,22 +250,22 @@
   <autoFilter ref="A1:F2" xr:uid="{219B2AB9-71B2-43D2-AE6E-1611D13DCF23}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{AD9B9425-01B9-40D9-AE72-DCBA99B5D621}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{059D2B67-4C83-46B2-B4BD-4EDE35F38133}" uniqueName="mon_pathId" name="mon_pathId">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_pathId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_pathId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{C1772F7D-DD8E-4A36-8690-D1347E3B9C42}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{99E00AF6-8AF3-496F-B170-52EB1B72FD9E}" uniqueName="mon_spawnId" name="mon_spawnId">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_spawnId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_spawnId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{82B7969F-C8B2-40F9-BD70-BD083F72D236}" uniqueName="mon_spawnTime" name="mon_spawnTime">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_spawnTime" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_spawnTime" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{990746DB-2815-4B16-8C7D-4B45AA5C32E1}" uniqueName="mon_spawnDayNight" name="mon_spawnDayNight">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/record/mon_spawnDayNight" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_spawnDayNight" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -277,34 +277,34 @@
   <autoFilter ref="A1:J7" xr:uid="{45C7799A-8301-4E60-B2D0-3DE51CA51E51}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{77EAA5DA-E1F1-421E-ACC8-93692512F11D}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8DBAF7B5-5E74-4090-92E0-20C16DFD816F}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{78F3970B-3EF8-4355-97B6-FB2E214E6683}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7E847E13-3429-4541-8B7B-6EDF5C718DD3}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{6E681DF7-C625-4327-BEB2-EB7DFE49CCF1}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{A51832D6-4DA9-400F-9ADB-89F73082B709}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{D2A8E0C7-292E-4CBA-B874-D84552D516DB}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{88DB5186-CA75-44DE-93BD-FD7BE3E772C3}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{25330282-8179-436F-8B54-8CEA5B97079F}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{795533A2-BE81-4D94-8F02-1FDF3308FE99}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="4" xpath="/monster_boss/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/monster_boss.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_boss.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38D8870A-2911-4A73-B069-19F0F30744B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{581B2EB4-7C95-433E-A109-406BCC2ACC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{56D7624B-7CB0-48D9-93FE-DC8F942FF1A2}"/>
   </bookViews>
@@ -241,7 +241,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="6" Name="monster_boss_맵" RootElement="monster_boss" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="8" Name="monster_boss_맵" RootElement="monster_boss" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -250,22 +250,22 @@
   <autoFilter ref="A1:F2" xr:uid="{219B2AB9-71B2-43D2-AE6E-1611D13DCF23}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{AD9B9425-01B9-40D9-AE72-DCBA99B5D621}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{059D2B67-4C83-46B2-B4BD-4EDE35F38133}" uniqueName="mon_pathId" name="mon_pathId">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_pathId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_pathId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{C1772F7D-DD8E-4A36-8690-D1347E3B9C42}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{99E00AF6-8AF3-496F-B170-52EB1B72FD9E}" uniqueName="mon_spawnId" name="mon_spawnId">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_spawnId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_spawnId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{82B7969F-C8B2-40F9-BD70-BD083F72D236}" uniqueName="mon_spawnTime" name="mon_spawnTime">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_spawnTime" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_spawnTime" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{990746DB-2815-4B16-8C7D-4B45AA5C32E1}" uniqueName="mon_spawnDayNight" name="mon_spawnDayNight">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/record/mon_spawnDayNight" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_spawnDayNight" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -277,34 +277,34 @@
   <autoFilter ref="A1:J7" xr:uid="{45C7799A-8301-4E60-B2D0-3DE51CA51E51}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{77EAA5DA-E1F1-421E-ACC8-93692512F11D}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8DBAF7B5-5E74-4090-92E0-20C16DFD816F}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{78F3970B-3EF8-4355-97B6-FB2E214E6683}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7E847E13-3429-4541-8B7B-6EDF5C718DD3}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{6E681DF7-C625-4327-BEB2-EB7DFE49CCF1}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{A51832D6-4DA9-400F-9ADB-89F73082B709}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{D2A8E0C7-292E-4CBA-B874-D84552D516DB}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{88DB5186-CA75-44DE-93BD-FD7BE3E772C3}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{25330282-8179-436F-8B54-8CEA5B97079F}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{795533A2-BE81-4D94-8F02-1FDF3308FE99}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="6" xpath="/monster_boss/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/monster_boss.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_boss.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{581B2EB4-7C95-433E-A109-406BCC2ACC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51A52FE1-8F86-4281-B431-C6AD6771DDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{56D7624B-7CB0-48D9-93FE-DC8F942FF1A2}"/>
   </bookViews>
@@ -241,7 +241,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="8" Name="monster_boss_맵" RootElement="monster_boss" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="monster_boss_맵" RootElement="monster_boss" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -250,22 +250,22 @@
   <autoFilter ref="A1:F2" xr:uid="{219B2AB9-71B2-43D2-AE6E-1611D13DCF23}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{AD9B9425-01B9-40D9-AE72-DCBA99B5D621}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{059D2B67-4C83-46B2-B4BD-4EDE35F38133}" uniqueName="mon_pathId" name="mon_pathId">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_pathId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/record/mon_pathId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{C1772F7D-DD8E-4A36-8690-D1347E3B9C42}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/record/mon_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{99E00AF6-8AF3-496F-B170-52EB1B72FD9E}" uniqueName="mon_spawnId" name="mon_spawnId">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_spawnId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/record/mon_spawnId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{82B7969F-C8B2-40F9-BD70-BD083F72D236}" uniqueName="mon_spawnTime" name="mon_spawnTime">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_spawnTime" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/record/mon_spawnTime" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{990746DB-2815-4B16-8C7D-4B45AA5C32E1}" uniqueName="mon_spawnDayNight" name="mon_spawnDayNight">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/record/mon_spawnDayNight" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/record/mon_spawnDayNight" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -277,34 +277,34 @@
   <autoFilter ref="A1:J7" xr:uid="{45C7799A-8301-4E60-B2D0-3DE51CA51E51}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{77EAA5DA-E1F1-421E-ACC8-93692512F11D}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8DBAF7B5-5E74-4090-92E0-20C16DFD816F}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{78F3970B-3EF8-4355-97B6-FB2E214E6683}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7E847E13-3429-4541-8B7B-6EDF5C718DD3}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{6E681DF7-C625-4327-BEB2-EB7DFE49CCF1}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{A51832D6-4DA9-400F-9ADB-89F73082B709}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{D2A8E0C7-292E-4CBA-B874-D84552D516DB}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{88DB5186-CA75-44DE-93BD-FD7BE3E772C3}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{25330282-8179-436F-8B54-8CEA5B97079F}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{795533A2-BE81-4D94-8F02-1FDF3308FE99}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="8" xpath="/monster_boss/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_boss/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
